--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>49308.13</v>
+        <v>49054.78</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19323.55</v>
+        <v>19224.27</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39714.76</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25544.79</v>
+        <v>25413.54</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25378.09</v>
+        <v>25124.81</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>74017.50999999999</v>
+        <v>73278.81</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>73415.60000000001</v>
+        <v>72646.78</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9407.09</v>
+        <v>9308.58</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24737.57</v>
+        <v>24602.36</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>24940.85</v>
+        <v>24804.53</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>71677.44</v>
+        <v>71285.66</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>47061.04</v>
+        <v>46536.71</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23914.52</v>
+        <v>23648.08</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>49881.7</v>
+        <v>49325.94</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>19236.99</v>
+        <v>19022.66</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>53398.29</v>
+        <v>52803.36</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37429.46</v>
+        <v>37224.48</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>142163.53</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="20">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>143418.47</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="21">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35851.44</v>
+        <v>35655.1</v>
       </c>
     </row>
     <row r="22">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>242295.64</v>
+        <v>240968.72</v>
       </c>
     </row>
     <row r="23">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26135.05</v>
+        <v>25991.92</v>
       </c>
     </row>
     <row r="24">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>53770.8</v>
+        <v>53702.36</v>
       </c>
     </row>
     <row r="25">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>57517.96</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="26">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>60791.01</v>
+        <v>60713.64</v>
       </c>
     </row>
     <row r="27">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>57517.96</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>73763.16</v>
+        <v>73669.27</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>53780.59</v>
+        <v>53972.52</v>
       </c>
     </row>
     <row r="30">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>28770.05</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="31">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>48734.55</v>
+        <v>48894.85</v>
       </c>
     </row>
     <row r="32">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>28770.05</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>210224.67</v>
+        <v>213853.47</v>
       </c>
     </row>
     <row r="34">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>238458.48</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="35">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24940.85</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="36">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>74291.3</v>
+        <v>74805.96000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>21718.56</v>
+        <v>21869.01</v>
       </c>
     </row>
     <row r="38">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>35877.83</v>
+        <v>36126.38</v>
       </c>
     </row>
     <row r="39">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>28758.98</v>
+        <v>28892.92</v>
       </c>
     </row>
     <row r="40">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>33348.28</v>
+        <v>33503.59</v>
       </c>
     </row>
     <row r="41">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>23952.6</v>
+        <v>24064.15</v>
       </c>
     </row>
     <row r="42">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>53807.51</v>
+        <v>54058.1</v>
       </c>
     </row>
     <row r="43">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>10284.62</v>
+        <v>10332.52</v>
       </c>
     </row>
     <row r="44">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>28758.98</v>
+        <v>28966.32</v>
       </c>
     </row>
     <row r="45">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>22604.31</v>
+        <v>22767.28</v>
       </c>
     </row>
     <row r="46">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>24710.66</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="47">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>57395.09</v>
+        <v>57808.88</v>
       </c>
     </row>
     <row r="48">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17156.29</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="49">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>25383.2</v>
+        <v>25338.18</v>
       </c>
     </row>
     <row r="50">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>29060.14</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="51">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29060.14</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="52">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>24940.85</v>
+        <v>24896.61</v>
       </c>
     </row>
     <row r="53">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>67279.63</v>
+        <v>67160.3</v>
       </c>
     </row>
     <row r="54">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>25383.2</v>
+        <v>25278.59</v>
       </c>
     </row>
     <row r="55">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>35766.48</v>
+        <v>35711.05</v>
       </c>
     </row>
     <row r="56">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>25276.22</v>
+        <v>25237.05</v>
       </c>
     </row>
     <row r="57">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>71532.96000000001</v>
+        <v>71422.09</v>
       </c>
     </row>
     <row r="58">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25856.53</v>
+        <v>25816.45</v>
       </c>
     </row>
     <row r="59">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>24023.9</v>
+        <v>23986.66</v>
       </c>
     </row>
     <row r="60">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>77787.06</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>19446.76</v>
+        <v>19547.2</v>
       </c>
     </row>
     <row r="62">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>73273.67999999999</v>
+        <v>73652.10000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="64">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>31111.44</v>
+        <v>31272.12</v>
       </c>
     </row>
     <row r="65">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41182.73</v>
+        <v>41395.42</v>
       </c>
     </row>
     <row r="66">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="67">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41640.32</v>
+        <v>41855.37</v>
       </c>
     </row>
     <row r="68">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>20704.55</v>
+        <v>20850.68</v>
       </c>
     </row>
     <row r="69">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>49881.7</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="70">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>29061.41</v>
+        <v>29266.52</v>
       </c>
     </row>
     <row r="71">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>48739.81</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="72">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>28758.98</v>
+        <v>28961.95</v>
       </c>
     </row>
     <row r="73">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>39714.76</v>
+        <v>39995.05</v>
       </c>
     </row>
     <row r="74">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>60791.01</v>
+        <v>61220.05</v>
       </c>
     </row>
     <row r="75">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>43687.79</v>
+        <v>43996.12</v>
       </c>
     </row>
     <row r="76">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>49881.7</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="77">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>17538.84</v>
+        <v>17662.63</v>
       </c>
     </row>
     <row r="78">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>45955.02</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="79">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>30447.88</v>
+        <v>30662.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1139,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1204,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1334,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1399,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1525,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1590,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1733,7 +1785,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1859,7 +1915,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1920,7 +1980,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1981,7 +2045,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2042,7 +2110,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2103,7 +2175,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2164,7 +2240,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2286,7 +2366,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2347,7 +2431,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2408,7 +2496,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2599,7 +2691,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2660,7 +2756,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2721,7 +2821,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2782,7 +2886,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2843,7 +2951,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2904,7 +3016,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2965,7 +3081,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3026,7 +3146,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3148,7 +3272,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3209,7 +3337,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3270,7 +3402,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3331,7 +3467,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3392,7 +3532,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3453,7 +3597,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3514,7 +3662,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3575,7 +3727,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3636,7 +3792,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3697,7 +3857,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3758,7 +3922,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3819,7 +3987,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3880,7 +4052,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3941,7 +4117,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4002,7 +4182,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4189,7 +4373,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4250,7 +4438,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4311,7 +4503,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4372,7 +4568,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4433,7 +4633,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4494,7 +4698,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4555,7 +4763,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4616,7 +4828,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4677,7 +4893,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4738,7 +4958,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4799,7 +5023,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4860,7 +5088,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4921,7 +5153,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4982,7 +5218,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5043,7 +5283,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5104,7 +5348,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5165,7 +5413,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5226,7 +5478,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5287,7 +5543,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
